--- a/template/机组花名册.xlsx
+++ b/template/机组花名册.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="373">
   <si>
     <t>员工号</t>
   </si>
@@ -170,6 +170,12 @@
     <t>阳志国</t>
   </si>
   <si>
+    <t>陈进军</t>
+  </si>
+  <si>
+    <t>张剑</t>
+  </si>
+  <si>
     <t>石桂平</t>
   </si>
   <si>
@@ -206,9 +212,6 @@
     <t>张鹏</t>
   </si>
   <si>
-    <t>张剑</t>
-  </si>
-  <si>
     <t>张岭</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
     <t>单国强</t>
   </si>
   <si>
-    <t>陈进军</t>
-  </si>
-  <si>
     <t>何晓东</t>
   </si>
   <si>
@@ -341,6 +341,9 @@
     <t>梁浩</t>
   </si>
   <si>
+    <t>杜虎</t>
+  </si>
+  <si>
     <t>陶炼</t>
   </si>
   <si>
@@ -362,9 +365,6 @@
     <t>冯志权</t>
   </si>
   <si>
-    <t>杜虎</t>
-  </si>
-  <si>
     <t>李旭波</t>
   </si>
   <si>
@@ -500,18 +500,21 @@
     <t>李益丞</t>
   </si>
   <si>
+    <t>王聪</t>
+  </si>
+  <si>
+    <t>李健</t>
+  </si>
+  <si>
+    <t>史东</t>
+  </si>
+  <si>
+    <t>王麒皓</t>
+  </si>
+  <si>
     <t>赵子超</t>
   </si>
   <si>
-    <t>王麒皓</t>
-  </si>
-  <si>
-    <t>史东</t>
-  </si>
-  <si>
-    <t>王聪</t>
-  </si>
-  <si>
     <t>朱磊</t>
   </si>
   <si>
@@ -521,9 +524,6 @@
     <t>萧瑞胜</t>
   </si>
   <si>
-    <t>李健</t>
-  </si>
-  <si>
     <t>莫文龙</t>
   </si>
   <si>
@@ -548,6 +548,12 @@
     <t>王家骝</t>
   </si>
   <si>
+    <t>李征征</t>
+  </si>
+  <si>
+    <t>朱皓</t>
+  </si>
+  <si>
     <t>钱少龙</t>
   </si>
   <si>
@@ -563,9 +569,6 @@
     <t>张寒义</t>
   </si>
   <si>
-    <t>朱皓</t>
-  </si>
-  <si>
     <t>崔玉柱</t>
   </si>
   <si>
@@ -608,9 +611,6 @@
     <t>贺万强</t>
   </si>
   <si>
-    <t>李征征</t>
-  </si>
-  <si>
     <t>张亚朋</t>
   </si>
   <si>
@@ -734,27 +734,27 @@
     <t>谢源</t>
   </si>
   <si>
+    <t>黄炳昊</t>
+  </si>
+  <si>
     <t>张星远</t>
   </si>
   <si>
+    <t>王晨旭</t>
+  </si>
+  <si>
     <t>陈兆铭</t>
   </si>
   <si>
     <t>周锐豪</t>
   </si>
   <si>
-    <t>黄炳昊</t>
-  </si>
-  <si>
     <t>刘洋</t>
   </si>
   <si>
     <t>陈俊</t>
   </si>
   <si>
-    <t>王晨旭</t>
-  </si>
-  <si>
     <t>周浩良</t>
   </si>
   <si>
@@ -860,6 +860,9 @@
     <t>陈健</t>
   </si>
   <si>
+    <t>李振洋</t>
+  </si>
+  <si>
     <t>沈铭</t>
   </si>
   <si>
@@ -908,9 +911,6 @@
     <t>胡博</t>
   </si>
   <si>
-    <t>李振洋</t>
-  </si>
-  <si>
     <t>杨登科</t>
   </si>
   <si>
@@ -989,12 +989,33 @@
     <t>朱丹浩</t>
   </si>
   <si>
+    <t>洪昭</t>
+  </si>
+  <si>
+    <t>陈嘉龙</t>
+  </si>
+  <si>
+    <t>尹翔</t>
+  </si>
+  <si>
+    <t>李恩豪</t>
+  </si>
+  <si>
+    <t>龙永峰</t>
+  </si>
+  <si>
+    <t>杨鲲鹏</t>
+  </si>
+  <si>
+    <t>刘观正</t>
+  </si>
+  <si>
+    <t>滕兆麟</t>
+  </si>
+  <si>
     <t>刘千里</t>
   </si>
   <si>
-    <t>刘观正</t>
-  </si>
-  <si>
     <t>王年鹏</t>
   </si>
   <si>
@@ -1004,9 +1025,6 @@
     <t>闫文平</t>
   </si>
   <si>
-    <t>尹翔</t>
-  </si>
-  <si>
     <t>张龙龙</t>
   </si>
   <si>
@@ -1022,21 +1040,9 @@
     <t>路舜锋</t>
   </si>
   <si>
-    <t>陈嘉龙</t>
-  </si>
-  <si>
-    <t>龙永峰</t>
-  </si>
-  <si>
     <t>张靖博</t>
   </si>
   <si>
-    <t>洪昭</t>
-  </si>
-  <si>
-    <t>李恩豪</t>
-  </si>
-  <si>
     <t>黄捷</t>
   </si>
   <si>
@@ -1058,12 +1064,6 @@
     <t>张成</t>
   </si>
   <si>
-    <t>杨鲲鹏</t>
-  </si>
-  <si>
-    <t>滕兆麟</t>
-  </si>
-  <si>
     <t>文强</t>
   </si>
   <si>
@@ -1116,6 +1116,36 @@
   </si>
   <si>
     <t>朱慕杰</t>
+  </si>
+  <si>
+    <t>吴智鑫</t>
+  </si>
+  <si>
+    <t>梁振</t>
+  </si>
+  <si>
+    <t>李正江</t>
+  </si>
+  <si>
+    <t>聂莘欣</t>
+  </si>
+  <si>
+    <t>桂宇博</t>
+  </si>
+  <si>
+    <t>孙金晨</t>
+  </si>
+  <si>
+    <t>罗浩诚</t>
+  </si>
+  <si>
+    <t>刘宇</t>
+  </si>
+  <si>
+    <t>寇西武</t>
+  </si>
+  <si>
+    <t>孔繁平</t>
   </si>
 </sst>
 </file>
@@ -2326,10 +2356,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B362"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B372"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="2" width="15.625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="15.6296296296296" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2702,7 +2732,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="3">
-        <v>191452</v>
+        <v>196267</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>47</v>
@@ -2710,7 +2740,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="3">
-        <v>208985</v>
+        <v>210541</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>48</v>
@@ -2718,7 +2748,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="3">
-        <v>206632</v>
+        <v>191452</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>49</v>
@@ -2726,7 +2756,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="3">
-        <v>199680</v>
+        <v>208985</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>50</v>
@@ -2734,7 +2764,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="3">
-        <v>181503</v>
+        <v>206632</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>51</v>
@@ -2742,7 +2772,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="3">
-        <v>181513</v>
+        <v>199680</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>52</v>
@@ -2750,7 +2780,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="3">
-        <v>181558</v>
+        <v>181503</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>53</v>
@@ -2758,7 +2788,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="3">
-        <v>181727</v>
+        <v>181513</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>54</v>
@@ -2766,7 +2796,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="3">
-        <v>186662</v>
+        <v>181558</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>55</v>
@@ -2774,7 +2804,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="3">
-        <v>193391</v>
+        <v>181727</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>56</v>
@@ -2782,7 +2812,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="3">
-        <v>201906</v>
+        <v>186662</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>57</v>
@@ -2790,7 +2820,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="3">
-        <v>202990</v>
+        <v>193391</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>58</v>
@@ -2798,7 +2828,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="3">
-        <v>210541</v>
+        <v>201906</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>59</v>
@@ -2806,7 +2836,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="3">
-        <v>901768</v>
+        <v>202990</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>60</v>
@@ -2814,7 +2844,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="3">
-        <v>201982</v>
+        <v>901768</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>61</v>
@@ -2822,7 +2852,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="3">
-        <v>210535</v>
+        <v>201982</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>62</v>
@@ -2830,7 +2860,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="3">
-        <v>905175</v>
+        <v>210535</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>63</v>
@@ -2838,7 +2868,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="3">
-        <v>196267</v>
+        <v>905175</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>64</v>
@@ -3092,7 +3122,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="96" ht="27" spans="1:2">
+    <row r="96" ht="43.2" spans="1:2">
       <c r="A96" s="6">
         <v>777575</v>
       </c>
@@ -3158,7 +3188,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="3">
-        <v>210510</v>
+        <v>216505</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>104</v>
@@ -3166,7 +3196,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="3">
-        <v>193177</v>
+        <v>210510</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>105</v>
@@ -3174,7 +3204,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="3">
-        <v>202989</v>
+        <v>193177</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>106</v>
@@ -3182,7 +3212,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="3">
-        <v>208978</v>
+        <v>202989</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>107</v>
@@ -3190,7 +3220,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="3">
-        <v>208984</v>
+        <v>208978</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>108</v>
@@ -3198,7 +3228,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="3">
-        <v>212810</v>
+        <v>208984</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>109</v>
@@ -3206,7 +3236,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="3">
-        <v>184767</v>
+        <v>212810</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>110</v>
@@ -3214,7 +3244,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="3">
-        <v>216505</v>
+        <v>184767</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>111</v>
@@ -3460,7 +3490,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="142" ht="40.5" spans="1:2">
+    <row r="142" ht="43.2" spans="1:2">
       <c r="A142" s="6">
         <v>263574</v>
       </c>
@@ -3548,7 +3578,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="153" ht="27" spans="1:2">
+    <row r="153" ht="28.8" spans="1:2">
       <c r="A153" s="6">
         <v>248809</v>
       </c>
@@ -3582,17 +3612,17 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="3">
-        <v>188592</v>
+        <v>217117</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="3">
-        <v>225674</v>
-      </c>
-      <c r="B158" s="4" t="s">
+      <c r="A158" s="6">
+        <v>901500</v>
+      </c>
+      <c r="B158" s="7" t="s">
         <v>158</v>
       </c>
     </row>
@@ -3606,41 +3636,41 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="3">
-        <v>217117</v>
+        <v>225674</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="6">
+      <c r="A161" s="3">
+        <v>188592</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="6">
         <v>209178</v>
       </c>
-      <c r="B161" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="3">
-        <v>234426</v>
-      </c>
-      <c r="B162" s="4" t="s">
+      <c r="B162" s="7" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="3">
-        <v>186664</v>
+        <v>234426</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="6">
-        <v>901500</v>
-      </c>
-      <c r="B164" s="7" t="s">
+      <c r="A164" s="3">
+        <v>186664</v>
+      </c>
+      <c r="B164" s="4" t="s">
         <v>164</v>
       </c>
     </row>
@@ -3709,24 +3739,24 @@
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="4">
-        <v>210625</v>
-      </c>
-      <c r="B173" s="4" t="s">
+      <c r="A173" s="6">
+        <v>192993</v>
+      </c>
+      <c r="B173" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="3">
-        <v>214908</v>
+        <v>210155</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="3">
-        <v>215073</v>
+      <c r="A175" s="4">
+        <v>210625</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>175</v>
@@ -3734,7 +3764,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="3">
-        <v>211318</v>
+        <v>214908</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>176</v>
@@ -3742,7 +3772,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="3">
-        <v>219807</v>
+        <v>215073</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>177</v>
@@ -3750,7 +3780,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="3">
-        <v>210155</v>
+        <v>211318</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>178</v>
@@ -3758,7 +3788,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="3">
-        <v>210787</v>
+        <v>219807</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>179</v>
@@ -3766,7 +3796,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="3">
-        <v>901756</v>
+        <v>210787</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>180</v>
@@ -3774,7 +3804,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="3">
-        <v>901557</v>
+        <v>901756</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>181</v>
@@ -3782,31 +3812,31 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="3">
-        <v>205130</v>
+        <v>901557</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="5">
+      <c r="A183" s="3">
+        <v>205130</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="5">
         <v>184790</v>
       </c>
-      <c r="B183" s="5" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="6">
-        <v>904950</v>
-      </c>
-      <c r="B184" s="7" t="s">
+      <c r="B184" s="5" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="6">
-        <v>211588</v>
+        <v>904950</v>
       </c>
       <c r="B185" s="7" t="s">
         <v>185</v>
@@ -3814,7 +3844,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="6">
-        <v>210135</v>
+        <v>211588</v>
       </c>
       <c r="B186" s="7" t="s">
         <v>186</v>
@@ -3822,7 +3852,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="6">
-        <v>210264</v>
+        <v>210135</v>
       </c>
       <c r="B187" s="7" t="s">
         <v>187</v>
@@ -3830,7 +3860,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="6">
-        <v>218359</v>
+        <v>210264</v>
       </c>
       <c r="B188" s="7" t="s">
         <v>188</v>
@@ -3838,7 +3868,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="6">
-        <v>211594</v>
+        <v>218359</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>189</v>
@@ -3846,7 +3876,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="6">
-        <v>224562</v>
+        <v>211594</v>
       </c>
       <c r="B190" s="7" t="s">
         <v>190</v>
@@ -3854,7 +3884,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="6">
-        <v>212815</v>
+        <v>224562</v>
       </c>
       <c r="B191" s="7" t="s">
         <v>191</v>
@@ -3862,7 +3892,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="6">
-        <v>189900</v>
+        <v>212815</v>
       </c>
       <c r="B192" s="7" t="s">
         <v>192</v>
@@ -3870,7 +3900,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="6">
-        <v>192993</v>
+        <v>189900</v>
       </c>
       <c r="B193" s="7" t="s">
         <v>193</v>
@@ -4206,7 +4236,7 @@
     </row>
     <row r="235" spans="1:2">
       <c r="A235" s="3">
-        <v>253776</v>
+        <v>266499</v>
       </c>
       <c r="B235" s="4" t="s">
         <v>235</v>
@@ -4214,7 +4244,7 @@
     </row>
     <row r="236" spans="1:2">
       <c r="A236" s="3">
-        <v>270784</v>
+        <v>253776</v>
       </c>
       <c r="B236" s="4" t="s">
         <v>236</v>
@@ -4222,7 +4252,7 @@
     </row>
     <row r="237" spans="1:2">
       <c r="A237" s="3">
-        <v>271943</v>
+        <v>270795</v>
       </c>
       <c r="B237" s="4" t="s">
         <v>237</v>
@@ -4230,7 +4260,7 @@
     </row>
     <row r="238" spans="1:2">
       <c r="A238" s="3">
-        <v>266499</v>
+        <v>270784</v>
       </c>
       <c r="B238" s="4" t="s">
         <v>238</v>
@@ -4238,7 +4268,7 @@
     </row>
     <row r="239" spans="1:2">
       <c r="A239" s="3">
-        <v>247695</v>
+        <v>271943</v>
       </c>
       <c r="B239" s="4" t="s">
         <v>239</v>
@@ -4246,7 +4276,7 @@
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="3">
-        <v>253781</v>
+        <v>247695</v>
       </c>
       <c r="B240" s="4" t="s">
         <v>240</v>
@@ -4254,7 +4284,7 @@
     </row>
     <row r="241" spans="1:2">
       <c r="A241" s="3">
-        <v>270795</v>
+        <v>253781</v>
       </c>
       <c r="B241" s="4" t="s">
         <v>241</v>
@@ -4541,8 +4571,8 @@
       </c>
     </row>
     <row r="277" spans="1:2">
-      <c r="A277" s="3">
-        <v>249564</v>
+      <c r="A277" s="4">
+        <v>283735</v>
       </c>
       <c r="B277" s="4" t="s">
         <v>277</v>
@@ -4550,7 +4580,7 @@
     </row>
     <row r="278" spans="1:2">
       <c r="A278" s="3">
-        <v>213858</v>
+        <v>249564</v>
       </c>
       <c r="B278" s="4" t="s">
         <v>278</v>
@@ -4558,15 +4588,15 @@
     </row>
     <row r="279" spans="1:2">
       <c r="A279" s="3">
-        <v>268097</v>
+        <v>213858</v>
       </c>
       <c r="B279" s="4" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="280" spans="1:2">
-      <c r="A280" s="4">
-        <v>276385</v>
+      <c r="A280" s="3">
+        <v>268097</v>
       </c>
       <c r="B280" s="4" t="s">
         <v>280</v>
@@ -4574,23 +4604,23 @@
     </row>
     <row r="281" spans="1:2">
       <c r="A281" s="4">
-        <v>281970</v>
+        <v>276385</v>
       </c>
       <c r="B281" s="4" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="282" spans="1:2">
-      <c r="A282" s="3">
-        <v>263409</v>
+      <c r="A282" s="4">
+        <v>281970</v>
       </c>
       <c r="B282" s="4" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="283" spans="1:2">
-      <c r="A283" s="4">
-        <v>210531</v>
+      <c r="A283" s="3">
+        <v>263409</v>
       </c>
       <c r="B283" s="4" t="s">
         <v>283</v>
@@ -4598,7 +4628,7 @@
     </row>
     <row r="284" spans="1:2">
       <c r="A284" s="4">
-        <v>276019</v>
+        <v>210531</v>
       </c>
       <c r="B284" s="4" t="s">
         <v>284</v>
@@ -4606,47 +4636,47 @@
     </row>
     <row r="285" spans="1:2">
       <c r="A285" s="4">
-        <v>215555</v>
+        <v>276019</v>
       </c>
       <c r="B285" s="4" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="286" spans="1:2">
-      <c r="A286" s="6">
+      <c r="A286" s="4">
+        <v>215555</v>
+      </c>
+      <c r="B286" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="6">
         <v>272827</v>
       </c>
-      <c r="B286" s="6" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="287" spans="1:2">
-      <c r="A287" s="3">
-        <v>279043</v>
-      </c>
-      <c r="B287" s="4" t="s">
+      <c r="B287" s="6" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" s="3">
-        <v>246465</v>
+        <v>279043</v>
       </c>
       <c r="B288" s="4" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="289" spans="1:2">
-      <c r="A289" s="4">
-        <v>261778</v>
+      <c r="A289" s="3">
+        <v>246465</v>
       </c>
       <c r="B289" s="4" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="290" spans="1:2">
-      <c r="A290" s="3">
-        <v>270788</v>
+      <c r="A290" s="4">
+        <v>261778</v>
       </c>
       <c r="B290" s="4" t="s">
         <v>290</v>
@@ -4654,15 +4684,15 @@
     </row>
     <row r="291" spans="1:2">
       <c r="A291" s="3">
-        <v>289953</v>
+        <v>270788</v>
       </c>
       <c r="B291" s="4" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="292" spans="1:2">
-      <c r="A292" s="4">
-        <v>285783</v>
+      <c r="A292" s="3">
+        <v>289953</v>
       </c>
       <c r="B292" s="4" t="s">
         <v>292</v>
@@ -4670,7 +4700,7 @@
     </row>
     <row r="293" spans="1:2">
       <c r="A293" s="4">
-        <v>283735</v>
+        <v>285783</v>
       </c>
       <c r="B293" s="4" t="s">
         <v>293</v>
@@ -4886,103 +4916,103 @@
     </row>
     <row r="320" spans="1:2">
       <c r="A320" s="4">
-        <v>217602</v>
+        <v>272821</v>
       </c>
       <c r="B320" s="4" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="321" spans="1:2">
-      <c r="A321" s="3">
-        <v>266461</v>
-      </c>
-      <c r="B321" s="4" t="s">
+      <c r="A321" s="6">
+        <v>285277</v>
+      </c>
+      <c r="B321" s="6" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" s="3">
-        <v>283749</v>
+        <v>284923</v>
       </c>
       <c r="B322" s="4" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="323" spans="1:2">
-      <c r="A323" s="3">
-        <v>284330</v>
-      </c>
-      <c r="B323" s="4" t="s">
+      <c r="A323" s="5">
+        <v>275104</v>
+      </c>
+      <c r="B323" s="5" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" s="3">
-        <v>284331</v>
+        <v>275006</v>
       </c>
       <c r="B324" s="4" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="325" spans="1:2">
-      <c r="A325" s="3">
-        <v>284923</v>
-      </c>
-      <c r="B325" s="4" t="s">
+      <c r="A325" s="6">
+        <v>294186</v>
+      </c>
+      <c r="B325" s="7" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" s="3">
-        <v>284332</v>
+        <v>266461</v>
       </c>
       <c r="B326" s="4" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="327" spans="1:2">
-      <c r="A327" s="3">
-        <v>275021</v>
-      </c>
-      <c r="B327" s="4" t="s">
+      <c r="A327" s="6">
+        <v>298237</v>
+      </c>
+      <c r="B327" s="7" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="328" spans="1:2">
-      <c r="A328" s="3">
-        <v>291033</v>
+      <c r="A328" s="4">
+        <v>217602</v>
       </c>
       <c r="B328" s="4" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="329" spans="1:2">
-      <c r="A329" s="6">
-        <v>285896</v>
-      </c>
-      <c r="B329" s="6" t="s">
+      <c r="A329" s="3">
+        <v>283749</v>
+      </c>
+      <c r="B329" s="4" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" s="3">
-        <v>286123</v>
+        <v>284330</v>
       </c>
       <c r="B330" s="4" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="331" spans="1:2">
-      <c r="A331" s="6">
-        <v>285277</v>
-      </c>
-      <c r="B331" s="6" t="s">
+      <c r="A331" s="3">
+        <v>284331</v>
+      </c>
+      <c r="B331" s="4" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="332" spans="1:2">
       <c r="A332" s="3">
-        <v>275006</v>
+        <v>284332</v>
       </c>
       <c r="B332" s="4" t="s">
         <v>332</v>
@@ -4990,63 +5020,63 @@
     </row>
     <row r="333" spans="1:2">
       <c r="A333" s="3">
-        <v>276056</v>
+        <v>275021</v>
       </c>
       <c r="B333" s="4" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="334" spans="1:2">
-      <c r="A334" s="4">
-        <v>272821</v>
+      <c r="A334" s="3">
+        <v>291033</v>
       </c>
       <c r="B334" s="4" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="335" spans="1:2">
-      <c r="A335" s="5">
-        <v>275104</v>
-      </c>
-      <c r="B335" s="5" t="s">
+      <c r="A335" s="6">
+        <v>285896</v>
+      </c>
+      <c r="B335" s="6" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="336" spans="1:2">
-      <c r="A336" s="5">
+      <c r="A336" s="3">
+        <v>286123</v>
+      </c>
+      <c r="B336" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="3">
+        <v>276056</v>
+      </c>
+      <c r="B337" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="5">
         <v>288902</v>
       </c>
-      <c r="B336" s="5" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2">
-      <c r="A337" s="5">
+      <c r="B338" s="5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="5">
         <v>289669</v>
       </c>
-      <c r="B337" s="5" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="338" spans="1:2">
-      <c r="A338" s="6">
-        <v>292765</v>
-      </c>
-      <c r="B338" s="7" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="339" spans="1:2">
-      <c r="A339" s="6">
-        <v>281004</v>
-      </c>
-      <c r="B339" s="7" t="s">
+      <c r="B339" s="5" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" s="6">
-        <v>278747</v>
+        <v>292765</v>
       </c>
       <c r="B340" s="7" t="s">
         <v>340</v>
@@ -5054,7 +5084,7 @@
     </row>
     <row r="341" spans="1:2">
       <c r="A341" s="6">
-        <v>263420</v>
+        <v>281004</v>
       </c>
       <c r="B341" s="7" t="s">
         <v>341</v>
@@ -5062,7 +5092,7 @@
     </row>
     <row r="342" spans="1:2">
       <c r="A342" s="6">
-        <v>271929</v>
+        <v>278747</v>
       </c>
       <c r="B342" s="7" t="s">
         <v>342</v>
@@ -5070,7 +5100,7 @@
     </row>
     <row r="343" spans="1:2">
       <c r="A343" s="6">
-        <v>294186</v>
+        <v>263420</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>343</v>
@@ -5078,7 +5108,7 @@
     </row>
     <row r="344" spans="1:2">
       <c r="A344" s="6">
-        <v>298237</v>
+        <v>271929</v>
       </c>
       <c r="B344" s="7" t="s">
         <v>344</v>
@@ -5228,8 +5258,88 @@
         <v>362</v>
       </c>
     </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="6">
+        <v>217693</v>
+      </c>
+      <c r="B363" s="7" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="6">
+        <v>217703</v>
+      </c>
+      <c r="B364" s="7" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="6">
+        <v>212877</v>
+      </c>
+      <c r="B365" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="6">
+        <v>306811</v>
+      </c>
+      <c r="B366" s="7" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="6">
+        <v>298838</v>
+      </c>
+      <c r="B367" s="7" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="6">
+        <v>302687</v>
+      </c>
+      <c r="B368" s="7" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="6">
+        <v>273284</v>
+      </c>
+      <c r="B369" s="7" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="6">
+        <v>905147</v>
+      </c>
+      <c r="B370" s="7" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="6">
+        <v>181764</v>
+      </c>
+      <c r="B371" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="6">
+        <v>706596</v>
+      </c>
+      <c r="B372" s="7" t="s">
+        <v>372</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B33 B37:B38 B47:B73 B45 B40:B41 B104:B134 B101 B345 B284:B285 B280:B281 B277:B278 B287:B288 B202:B208 B299:B306 B262:B264 B363:B1048576 B343 B213 B309 B271 B314 B82 B215:B226 B230:B233 B235:B248 B182 B162:B163 B168:B169 B165:B166 B186:B192 B146:B148 B84:B85 B173 B88 B76:B80 B316:B328 B137:B140 B99 B155:B159 B150:B152">
+  <conditionalFormatting sqref="B1:B33 B37:B38 B288:B289 B47:B73 B281:B282 B285:B286 B278:B279 B45 B40:B41 B328:B334 B104:B134 B325:B326 B101 B345 B373:B1048576 B168:B169 B84:B85 B146:B148 B202:B208 B299:B306 B262:B264 B159:B161 B175 B137:B140 B99 B187:B193 B213 B309 B271 B314 B82 B215:B226 B230:B233 B150:B152 B235:B248 B155:B156 B163:B166 B316:B319 B88 B322 B76:B80 B183">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
